--- a/artfynd/A 37131-2021 artfynd.xlsx
+++ b/artfynd/A 37131-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131840965</v>
       </c>
       <c r="B2" t="n">
-        <v>57806</v>
+        <v>57807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37131-2021 artfynd.xlsx
+++ b/artfynd/A 37131-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131840965</v>
       </c>
       <c r="B2" t="n">
-        <v>57807</v>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37131-2021 artfynd.xlsx
+++ b/artfynd/A 37131-2021 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>131840965</v>
       </c>
       <c r="B2" t="n">
-        <v>57816</v>
+        <v>57833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
